--- a/Task Report/Work item list/work list excell/Pending tasks.xlsx
+++ b/Task Report/Work item list/work list excell/Pending tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shahid Raza\Capitall\VSA project functionality\Task Report\Work item list\work list excell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF90773E-E670-41AF-980E-D03B3B3C46F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9EF1C0-C4E6-429E-B3FA-28FB32710806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{65BD65AB-347B-4BAB-9C5F-30C021D0C3BE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Client list edit functionality on the assignment view page</t>
   </si>
   <si>
-    <t>working (5 dayes)</t>
-  </si>
-  <si>
     <t>In QA tasks</t>
   </si>
   <si>
@@ -126,6 +123,18 @@
   </si>
   <si>
     <t>Not Approved Tasks</t>
+  </si>
+  <si>
+    <t>today will be live on demo</t>
+  </si>
+  <si>
+    <t>Pending Bugs</t>
+  </si>
+  <si>
+    <t>The bugs is date enable problem for 2 users when multiple leave applied.</t>
+  </si>
+  <si>
+    <t>1 days</t>
   </si>
 </sst>
 </file>
@@ -595,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAC6D6C0-AD37-4D97-8537-BFB732A57384}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.1796875" customWidth="1"/>
@@ -635,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -649,7 +658,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -663,7 +672,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -677,7 +686,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -691,10 +700,10 @@
         <v>2</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -702,7 +711,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D8" s="6"/>
     </row>
@@ -711,16 +720,18 @@
         <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="6">
         <v>7</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C11" s="6"/>
+    </row>
     <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>0</v>
@@ -728,153 +739,181 @@
       <c r="B12" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C12" s="6"/>
     </row>
     <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="4"/>
       <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C13" s="6"/>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4">
         <v>1</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="4">
-        <v>2</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="4">
-        <v>3</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="4">
-        <v>4</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+        <v>31</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="21" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5" t="s">
-        <v>16</v>
+      <c r="B22" s="7" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4">
+        <v>2</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="4">
+        <v>3</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="4">
+        <v>4</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="29" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="26" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="4">
-        <v>1</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="4">
-        <v>2</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="4">
-        <v>3</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>22</v>
+      <c r="A30" s="4"/>
+      <c r="B30" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="4">
-        <v>5</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="4">
-        <v>6</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="4">
-        <v>7</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>26</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="34" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="4">
-        <v>8</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>27</v>
+      <c r="A35" s="4"/>
+      <c r="B35" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="4">
+        <v>1</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="4">
+        <v>2</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="4">
+        <v>3</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="4">
+        <v>4</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="4">
+        <v>5</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="4">
+        <v>6</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="4">
+        <v>7</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="4">
+        <v>8</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="4">
         <v>9</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>28</v>
+      <c r="B44" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
